--- a/策划/excel/7_RoleCard.xlsx
+++ b/策划/excel/7_RoleCard.xlsx
@@ -348,7 +348,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D103"/>
   <sheetFormatPr defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="3" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -428,13 +428,13 @@
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
-        <v>70001</v>
+        <v>70011</v>
       </c>
       <c r="B6" s="1">
-        <v>10001</v>
+        <v>10002</v>
       </c>
       <c r="C6" s="1">
-        <v>20001</v>
+        <v>20011</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -442,13 +442,13 @@
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
-        <v>70002</v>
+        <v>70012</v>
       </c>
       <c r="B7" s="1">
-        <v>10001</v>
+        <v>10002</v>
       </c>
       <c r="C7" s="1">
-        <v>20002</v>
+        <v>20012</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -456,13 +456,13 @@
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
-        <v>70003</v>
+        <v>70013</v>
       </c>
       <c r="B8" s="1">
-        <v>10001</v>
+        <v>10002</v>
       </c>
       <c r="C8" s="1">
-        <v>20003</v>
+        <v>20013</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -470,13 +470,13 @@
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
-        <v>70004</v>
+        <v>70014</v>
       </c>
       <c r="B9" s="1">
-        <v>10001</v>
+        <v>10002</v>
       </c>
       <c r="C9" s="1">
-        <v>20004</v>
+        <v>20014</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -484,13 +484,13 @@
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
-        <v>70005</v>
+        <v>70015</v>
       </c>
       <c r="B10" s="1">
-        <v>10001</v>
+        <v>10002</v>
       </c>
       <c r="C10" s="1">
-        <v>20005</v>
+        <v>20015</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -498,13 +498,13 @@
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
-        <v>70006</v>
+        <v>70016</v>
       </c>
       <c r="B11" s="1">
-        <v>10001</v>
+        <v>10002</v>
       </c>
       <c r="C11" s="1">
-        <v>20006</v>
+        <v>20016</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -512,13 +512,13 @@
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
-        <v>70007</v>
+        <v>70017</v>
       </c>
       <c r="B12" s="1">
-        <v>10001</v>
+        <v>10002</v>
       </c>
       <c r="C12" s="1">
-        <v>20007</v>
+        <v>20017</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -526,13 +526,13 @@
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
-        <v>70008</v>
+        <v>70018</v>
       </c>
       <c r="B13" s="1">
-        <v>10001</v>
+        <v>10002</v>
       </c>
       <c r="C13" s="1">
-        <v>20008</v>
+        <v>20018</v>
       </c>
       <c r="D13">
         <v>2</v>
@@ -540,13 +540,13 @@
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
-        <v>70009</v>
+        <v>70019</v>
       </c>
       <c r="B14" s="1">
-        <v>10001</v>
+        <v>10002</v>
       </c>
       <c r="C14" s="1">
-        <v>20009</v>
+        <v>20019</v>
       </c>
       <c r="D14">
         <v>2</v>
@@ -554,13 +554,13 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>70010</v>
+        <v>70020</v>
       </c>
       <c r="B15">
-        <v>10001</v>
+        <v>10002</v>
       </c>
       <c r="C15">
-        <v>20010</v>
+        <v>20020</v>
       </c>
       <c r="D15">
         <v>2</v>
@@ -568,13 +568,13 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>70011</v>
+        <v>70021</v>
       </c>
       <c r="B16">
-        <v>10002</v>
+        <v>10003</v>
       </c>
       <c r="C16">
-        <v>20011</v>
+        <v>20021</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -582,13 +582,13 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>70012</v>
+        <v>70022</v>
       </c>
       <c r="B17">
-        <v>10002</v>
+        <v>10003</v>
       </c>
       <c r="C17">
-        <v>20012</v>
+        <v>20022</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -596,13 +596,13 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>70013</v>
+        <v>70023</v>
       </c>
       <c r="B18">
-        <v>10002</v>
+        <v>10003</v>
       </c>
       <c r="C18">
-        <v>20013</v>
+        <v>20023</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -610,13 +610,13 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>70014</v>
+        <v>70024</v>
       </c>
       <c r="B19">
-        <v>10002</v>
+        <v>10003</v>
       </c>
       <c r="C19">
-        <v>20014</v>
+        <v>20024</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -624,13 +624,13 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>70015</v>
+        <v>70025</v>
       </c>
       <c r="B20">
-        <v>10002</v>
+        <v>10003</v>
       </c>
       <c r="C20">
-        <v>20015</v>
+        <v>20025</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -638,13 +638,13 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>70016</v>
+        <v>70026</v>
       </c>
       <c r="B21">
-        <v>10002</v>
+        <v>10003</v>
       </c>
       <c r="C21">
-        <v>20016</v>
+        <v>20026</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -652,13 +652,13 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>70017</v>
+        <v>70027</v>
       </c>
       <c r="B22">
-        <v>10002</v>
+        <v>10003</v>
       </c>
       <c r="C22">
-        <v>20017</v>
+        <v>20027</v>
       </c>
       <c r="D22">
         <v>1</v>
@@ -666,13 +666,13 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>70018</v>
+        <v>70028</v>
       </c>
       <c r="B23">
-        <v>10002</v>
+        <v>10003</v>
       </c>
       <c r="C23">
-        <v>20018</v>
+        <v>20028</v>
       </c>
       <c r="D23">
         <v>2</v>
@@ -680,13 +680,13 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>70019</v>
+        <v>70029</v>
       </c>
       <c r="B24">
-        <v>10002</v>
+        <v>10003</v>
       </c>
       <c r="C24">
-        <v>20019</v>
+        <v>20029</v>
       </c>
       <c r="D24">
         <v>2</v>
@@ -694,13 +694,13 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>70020</v>
+        <v>70030</v>
       </c>
       <c r="B25">
-        <v>10002</v>
+        <v>10003</v>
       </c>
       <c r="C25">
-        <v>20020</v>
+        <v>20030</v>
       </c>
       <c r="D25">
         <v>2</v>
@@ -708,13 +708,13 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>70021</v>
+        <v>70031</v>
       </c>
       <c r="B26">
-        <v>10003</v>
+        <v>10001</v>
       </c>
       <c r="C26">
-        <v>20021</v>
+        <v>20031</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -722,13 +722,13 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>70022</v>
+        <v>70032</v>
       </c>
       <c r="B27">
-        <v>10003</v>
+        <v>10001</v>
       </c>
       <c r="C27">
-        <v>20022</v>
+        <v>20032</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -736,13 +736,13 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>70023</v>
+        <v>70033</v>
       </c>
       <c r="B28">
-        <v>10003</v>
+        <v>10001</v>
       </c>
       <c r="C28">
-        <v>20023</v>
+        <v>20033</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -750,13 +750,13 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>70024</v>
+        <v>70034</v>
       </c>
       <c r="B29">
-        <v>10003</v>
+        <v>10001</v>
       </c>
       <c r="C29">
-        <v>20024</v>
+        <v>20034</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -764,85 +764,1037 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>70025</v>
+        <v>70035</v>
       </c>
       <c r="B30">
-        <v>10003</v>
+        <v>10001</v>
       </c>
       <c r="C30">
-        <v>20025</v>
+        <v>20035</v>
       </c>
       <c r="D30">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>70026</v>
+        <v>70036</v>
       </c>
       <c r="B31">
-        <v>10003</v>
+        <v>10001</v>
       </c>
       <c r="C31">
-        <v>20026</v>
+        <v>20036</v>
       </c>
       <c r="D31">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>70027</v>
+        <v>70037</v>
       </c>
       <c r="B32">
-        <v>10003</v>
+        <v>10001</v>
       </c>
       <c r="C32">
-        <v>20027</v>
+        <v>20037</v>
       </c>
       <c r="D32">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>70028</v>
+        <v>70038</v>
       </c>
       <c r="B33">
-        <v>10003</v>
+        <v>10001</v>
       </c>
       <c r="C33">
-        <v>20028</v>
+        <v>20038</v>
       </c>
       <c r="D33">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>70029</v>
+        <v>70039</v>
       </c>
       <c r="B34">
-        <v>10003</v>
+        <v>10001</v>
       </c>
       <c r="C34">
-        <v>20029</v>
+        <v>20039</v>
       </c>
       <c r="D34">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>70030</v>
+        <v>70040</v>
       </c>
       <c r="B35">
-        <v>10003</v>
+        <v>10001</v>
       </c>
       <c r="C35">
-        <v>20030</v>
+        <v>20040</v>
       </c>
       <c r="D35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>70041</v>
+      </c>
+      <c r="B36">
+        <v>10001</v>
+      </c>
+      <c r="C36">
+        <v>20041</v>
+      </c>
+      <c r="D36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>70042</v>
+      </c>
+      <c r="B37">
+        <v>10001</v>
+      </c>
+      <c r="C37">
+        <v>20042</v>
+      </c>
+      <c r="D37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>70043</v>
+      </c>
+      <c r="B38">
+        <v>10001</v>
+      </c>
+      <c r="C38">
+        <v>20043</v>
+      </c>
+      <c r="D38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>70044</v>
+      </c>
+      <c r="B39">
+        <v>10001</v>
+      </c>
+      <c r="C39">
+        <v>20044</v>
+      </c>
+      <c r="D39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>70045</v>
+      </c>
+      <c r="B40">
+        <v>10001</v>
+      </c>
+      <c r="C40">
+        <v>20045</v>
+      </c>
+      <c r="D40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>70046</v>
+      </c>
+      <c r="B41">
+        <v>10001</v>
+      </c>
+      <c r="C41">
+        <v>20046</v>
+      </c>
+      <c r="D41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>70047</v>
+      </c>
+      <c r="B42">
+        <v>10001</v>
+      </c>
+      <c r="C42">
+        <v>20048</v>
+      </c>
+      <c r="D42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>70048</v>
+      </c>
+      <c r="B43">
+        <v>10001</v>
+      </c>
+      <c r="C43">
+        <v>20049</v>
+      </c>
+      <c r="D43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>70049</v>
+      </c>
+      <c r="B44">
+        <v>10001</v>
+      </c>
+      <c r="C44">
+        <v>20050</v>
+      </c>
+      <c r="D44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>70050</v>
+      </c>
+      <c r="B45">
+        <v>10001</v>
+      </c>
+      <c r="C45">
+        <v>20051</v>
+      </c>
+      <c r="D45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>70051</v>
+      </c>
+      <c r="B46">
+        <v>10001</v>
+      </c>
+      <c r="C46">
+        <v>20052</v>
+      </c>
+      <c r="D46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>70052</v>
+      </c>
+      <c r="B47">
+        <v>10001</v>
+      </c>
+      <c r="C47">
+        <v>20053</v>
+      </c>
+      <c r="D47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>70053</v>
+      </c>
+      <c r="B48">
+        <v>10001</v>
+      </c>
+      <c r="C48">
+        <v>20054</v>
+      </c>
+      <c r="D48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>70054</v>
+      </c>
+      <c r="B49">
+        <v>10001</v>
+      </c>
+      <c r="C49">
+        <v>20055</v>
+      </c>
+      <c r="D49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>70055</v>
+      </c>
+      <c r="B50">
+        <v>10001</v>
+      </c>
+      <c r="C50">
+        <v>20056</v>
+      </c>
+      <c r="D50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>70056</v>
+      </c>
+      <c r="B51">
+        <v>10001</v>
+      </c>
+      <c r="C51">
+        <v>20057</v>
+      </c>
+      <c r="D51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>70057</v>
+      </c>
+      <c r="B52">
+        <v>10001</v>
+      </c>
+      <c r="C52">
+        <v>20058</v>
+      </c>
+      <c r="D52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>70058</v>
+      </c>
+      <c r="B53">
+        <v>10001</v>
+      </c>
+      <c r="C53">
+        <v>20059</v>
+      </c>
+      <c r="D53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>70059</v>
+      </c>
+      <c r="B54">
+        <v>10001</v>
+      </c>
+      <c r="C54">
+        <v>20060</v>
+      </c>
+      <c r="D54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>70060</v>
+      </c>
+      <c r="B55">
+        <v>10001</v>
+      </c>
+      <c r="C55">
+        <v>20061</v>
+      </c>
+      <c r="D55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>70061</v>
+      </c>
+      <c r="B56">
+        <v>10001</v>
+      </c>
+      <c r="C56">
+        <v>20062</v>
+      </c>
+      <c r="D56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>70062</v>
+      </c>
+      <c r="B57">
+        <v>10001</v>
+      </c>
+      <c r="C57">
+        <v>20063</v>
+      </c>
+      <c r="D57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>70063</v>
+      </c>
+      <c r="B58">
+        <v>10001</v>
+      </c>
+      <c r="C58">
+        <v>20064</v>
+      </c>
+      <c r="D58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>70064</v>
+      </c>
+      <c r="B59">
+        <v>10001</v>
+      </c>
+      <c r="C59">
+        <v>20065</v>
+      </c>
+      <c r="D59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>70065</v>
+      </c>
+      <c r="B60">
+        <v>10001</v>
+      </c>
+      <c r="C60">
+        <v>20066</v>
+      </c>
+      <c r="D60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>70066</v>
+      </c>
+      <c r="B61">
+        <v>10001</v>
+      </c>
+      <c r="C61">
+        <v>20067</v>
+      </c>
+      <c r="D61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>70067</v>
+      </c>
+      <c r="B62">
+        <v>10001</v>
+      </c>
+      <c r="C62">
+        <v>20068</v>
+      </c>
+      <c r="D62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>70068</v>
+      </c>
+      <c r="B63">
+        <v>10001</v>
+      </c>
+      <c r="C63">
+        <v>20069</v>
+      </c>
+      <c r="D63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>70069</v>
+      </c>
+      <c r="B64">
+        <v>10001</v>
+      </c>
+      <c r="C64">
+        <v>20070</v>
+      </c>
+      <c r="D64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>70070</v>
+      </c>
+      <c r="B65">
+        <v>10001</v>
+      </c>
+      <c r="C65">
+        <v>20071</v>
+      </c>
+      <c r="D65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>70071</v>
+      </c>
+      <c r="B66">
+        <v>10001</v>
+      </c>
+      <c r="C66">
+        <v>20072</v>
+      </c>
+      <c r="D66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>70072</v>
+      </c>
+      <c r="B67">
+        <v>10001</v>
+      </c>
+      <c r="C67">
+        <v>20073</v>
+      </c>
+      <c r="D67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>70073</v>
+      </c>
+      <c r="B68">
+        <v>10001</v>
+      </c>
+      <c r="C68">
+        <v>20074</v>
+      </c>
+      <c r="D68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>70074</v>
+      </c>
+      <c r="B69">
+        <v>10001</v>
+      </c>
+      <c r="C69">
+        <v>20075</v>
+      </c>
+      <c r="D69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>70075</v>
+      </c>
+      <c r="B70">
+        <v>10001</v>
+      </c>
+      <c r="C70">
+        <v>20076</v>
+      </c>
+      <c r="D70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>70076</v>
+      </c>
+      <c r="B71">
+        <v>10001</v>
+      </c>
+      <c r="C71">
+        <v>20077</v>
+      </c>
+      <c r="D71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>70077</v>
+      </c>
+      <c r="B72">
+        <v>10001</v>
+      </c>
+      <c r="C72">
+        <v>20078</v>
+      </c>
+      <c r="D72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>70078</v>
+      </c>
+      <c r="B73">
+        <v>10001</v>
+      </c>
+      <c r="C73">
+        <v>20079</v>
+      </c>
+      <c r="D73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>70079</v>
+      </c>
+      <c r="B74">
+        <v>10001</v>
+      </c>
+      <c r="C74">
+        <v>20080</v>
+      </c>
+      <c r="D74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>70080</v>
+      </c>
+      <c r="B75">
+        <v>10001</v>
+      </c>
+      <c r="C75">
+        <v>20081</v>
+      </c>
+      <c r="D75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>70081</v>
+      </c>
+      <c r="B76">
+        <v>10001</v>
+      </c>
+      <c r="C76">
+        <v>20082</v>
+      </c>
+      <c r="D76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>70082</v>
+      </c>
+      <c r="B77">
+        <v>10001</v>
+      </c>
+      <c r="C77">
+        <v>20083</v>
+      </c>
+      <c r="D77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>70083</v>
+      </c>
+      <c r="B78">
+        <v>10001</v>
+      </c>
+      <c r="C78">
+        <v>20084</v>
+      </c>
+      <c r="D78">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>70084</v>
+      </c>
+      <c r="B79">
+        <v>10001</v>
+      </c>
+      <c r="C79">
+        <v>20085</v>
+      </c>
+      <c r="D79">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>70085</v>
+      </c>
+      <c r="B80">
+        <v>10001</v>
+      </c>
+      <c r="C80">
+        <v>20086</v>
+      </c>
+      <c r="D80">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>70086</v>
+      </c>
+      <c r="B81">
+        <v>10001</v>
+      </c>
+      <c r="C81">
+        <v>20087</v>
+      </c>
+      <c r="D81">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>70087</v>
+      </c>
+      <c r="B82">
+        <v>10001</v>
+      </c>
+      <c r="C82">
+        <v>20088</v>
+      </c>
+      <c r="D82">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>70088</v>
+      </c>
+      <c r="B83">
+        <v>10001</v>
+      </c>
+      <c r="C83">
+        <v>20089</v>
+      </c>
+      <c r="D83">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>70089</v>
+      </c>
+      <c r="B84">
+        <v>10001</v>
+      </c>
+      <c r="C84">
+        <v>20090</v>
+      </c>
+      <c r="D84">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>70090</v>
+      </c>
+      <c r="B85">
+        <v>10001</v>
+      </c>
+      <c r="C85">
+        <v>20091</v>
+      </c>
+      <c r="D85">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>70091</v>
+      </c>
+      <c r="B86">
+        <v>10001</v>
+      </c>
+      <c r="C86">
+        <v>20092</v>
+      </c>
+      <c r="D86">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>70092</v>
+      </c>
+      <c r="B87">
+        <v>10001</v>
+      </c>
+      <c r="C87">
+        <v>20093</v>
+      </c>
+      <c r="D87">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>70093</v>
+      </c>
+      <c r="B88">
+        <v>10001</v>
+      </c>
+      <c r="C88">
+        <v>20094</v>
+      </c>
+      <c r="D88">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>70094</v>
+      </c>
+      <c r="B89">
+        <v>10001</v>
+      </c>
+      <c r="C89">
+        <v>20095</v>
+      </c>
+      <c r="D89">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>70095</v>
+      </c>
+      <c r="B90">
+        <v>10001</v>
+      </c>
+      <c r="C90">
+        <v>20096</v>
+      </c>
+      <c r="D90">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>70096</v>
+      </c>
+      <c r="B91">
+        <v>10001</v>
+      </c>
+      <c r="C91">
+        <v>20097</v>
+      </c>
+      <c r="D91">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>70097</v>
+      </c>
+      <c r="B92">
+        <v>10001</v>
+      </c>
+      <c r="C92">
+        <v>20098</v>
+      </c>
+      <c r="D92">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>70098</v>
+      </c>
+      <c r="B93">
+        <v>10001</v>
+      </c>
+      <c r="C93">
+        <v>20099</v>
+      </c>
+      <c r="D93">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>70099</v>
+      </c>
+      <c r="B94">
+        <v>10001</v>
+      </c>
+      <c r="C94">
+        <v>20100</v>
+      </c>
+      <c r="D94">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>70100</v>
+      </c>
+      <c r="B95">
+        <v>10001</v>
+      </c>
+      <c r="C95">
+        <v>20101</v>
+      </c>
+      <c r="D95">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>70101</v>
+      </c>
+      <c r="B96">
+        <v>10001</v>
+      </c>
+      <c r="C96">
+        <v>20102</v>
+      </c>
+      <c r="D96">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>70102</v>
+      </c>
+      <c r="B97">
+        <v>10001</v>
+      </c>
+      <c r="C97">
+        <v>20103</v>
+      </c>
+      <c r="D97">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>70103</v>
+      </c>
+      <c r="B98">
+        <v>10001</v>
+      </c>
+      <c r="C98">
+        <v>20104</v>
+      </c>
+      <c r="D98">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>70104</v>
+      </c>
+      <c r="B99">
+        <v>10001</v>
+      </c>
+      <c r="C99">
+        <v>20105</v>
+      </c>
+      <c r="D99">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>70105</v>
+      </c>
+      <c r="B100">
+        <v>10001</v>
+      </c>
+      <c r="C100">
+        <v>20106</v>
+      </c>
+      <c r="D100">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>70106</v>
+      </c>
+      <c r="B101">
+        <v>10001</v>
+      </c>
+      <c r="C101">
+        <v>20107</v>
+      </c>
+      <c r="D101">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>70107</v>
+      </c>
+      <c r="B102">
+        <v>10001</v>
+      </c>
+      <c r="C102">
+        <v>20108</v>
+      </c>
+      <c r="D102">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>70108</v>
+      </c>
+      <c r="B103">
+        <v>10001</v>
+      </c>
+      <c r="C103">
+        <v>20109</v>
+      </c>
+      <c r="D103">
         <v>2</v>
       </c>
     </row>
